--- a/files/excel-mastery-2-4.xlsx
+++ b/files/excel-mastery-2-4.xlsx
@@ -543,7 +543,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
     <xf numFmtId="38" fontId="10" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -551,8 +551,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="9" fontId="10" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="202">
+  <cellXfs count="204">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -649,9 +652,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -706,21 +706,12 @@
     <xf numFmtId="165" fontId="9" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="3" fontId="6" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="3" fontId="6" fillId="5" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="3" fontId="6" fillId="5" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -733,29 +724,8 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="13" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="center"/>
@@ -871,160 +841,314 @@
     <xf numFmtId="0" fontId="27" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="16" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="16" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="16" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="24" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="24" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="24" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="24" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="16" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="25" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="17" fillId="4" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="17" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="12" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="17" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="28" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="28" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="22" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="13" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="13" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="13" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="16" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="28" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="28" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="28" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="23" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="23" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="16" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="13" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="13" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="13" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="13" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="13" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="23" fillId="3" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="23" fillId="3" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="23" fillId="3" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="16" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="24" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="16" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="16" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="24" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="24" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="24" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="13" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="24" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="16" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="25" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="17" fillId="4" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="17" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="12" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="165" fontId="22" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="165" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -1034,122 +1158,12 @@
     <xf numFmtId="165" fontId="17" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="28" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="28" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="22" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="13" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="13" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="13" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="9" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="16" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="28" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="28" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="28" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="23" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="23" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="23" fillId="3" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="23" fillId="3" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="23" fillId="3" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="16" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="24" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="17" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="4">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
     <cellStyle name="桁区切り" xfId="1" builtinId="6"/>
     <cellStyle name="標準 2" xfId="2"/>
+    <cellStyle name="パーセント" xfId="3" builtinId="5"/>
   </cellStyles>
   <dxfs count="6">
     <dxf>
@@ -1589,220 +1603,220 @@
   <dimension ref="B2:F24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13"/>
   <cols>
-    <col width="2.36328125" customWidth="1" style="158" min="1" max="3"/>
-    <col width="28" customWidth="1" style="158" min="4" max="4"/>
-    <col width="14" customWidth="1" style="158" min="5" max="5"/>
-    <col width="10" customWidth="1" style="158" min="6" max="6"/>
+    <col width="2.36328125" customWidth="1" min="1" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="2" ht="19.5" customHeight="1" s="158">
-      <c r="B2" s="75" t="inlineStr">
+    <row r="2" ht="19.5" customHeight="1">
+      <c r="B2" s="64" t="inlineStr">
         <is>
           <t>2-4. PLシミュレーション ①Input（前提・青字が入力）</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="13.5" customHeight="1" s="158"/>
-    <row r="4" ht="13.5" customHeight="1" s="158">
+    <row r="3" ht="13.5" customHeight="1"/>
+    <row r="4" ht="13.5" customHeight="1">
       <c r="D4" s="3" t="inlineStr">
         <is>
           <t>青字のセルだけを変更すれば、②計算・③Outputが自動で更新されます。</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="13.5" customHeight="1" s="158">
-      <c r="D5" s="77" t="inlineStr">
+    <row r="5" ht="13.5" customHeight="1">
+      <c r="D5" s="66" t="inlineStr">
         <is>
           <t>【売上ドライバー】</t>
         </is>
       </c>
-      <c r="E5" s="78" t="n"/>
-      <c r="F5" s="78" t="n"/>
-    </row>
-    <row r="6" ht="13.5" customHeight="1" s="158"/>
-    <row r="7" ht="13.5" customHeight="1" s="158">
-      <c r="D7" s="168" t="inlineStr">
+      <c r="E5" s="67" t="n"/>
+      <c r="F5" s="67" t="n"/>
+    </row>
+    <row r="6" ht="13.5" customHeight="1"/>
+    <row r="7" ht="13.5" customHeight="1">
+      <c r="D7" s="68" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="E7" s="168" t="inlineStr">
+      <c r="E7" s="68" t="inlineStr">
         <is>
           <t>値</t>
         </is>
       </c>
-      <c r="F7" s="168" t="inlineStr">
+      <c r="F7" s="68" t="inlineStr">
         <is>
           <t>単位</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="13.5" customHeight="1" s="158">
-      <c r="D8" s="80" t="inlineStr">
+    <row r="8" ht="13.5" customHeight="1">
+      <c r="D8" s="69" t="inlineStr">
         <is>
           <t>客室数</t>
         </is>
       </c>
-      <c r="E8" s="87" t="n">
+      <c r="E8" s="76" t="n">
         <v>20</v>
       </c>
-      <c r="F8" s="88" t="inlineStr">
+      <c r="F8" s="77" t="inlineStr">
         <is>
           <t>室</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="13.5" customHeight="1" s="158">
-      <c r="D9" s="83" t="inlineStr">
+    <row r="9" ht="13.5" customHeight="1">
+      <c r="D9" s="72" t="inlineStr">
         <is>
           <t>営業日数</t>
         </is>
       </c>
-      <c r="E9" s="89" t="n">
+      <c r="E9" s="78" t="n">
         <v>365</v>
       </c>
-      <c r="F9" s="90" t="inlineStr">
+      <c r="F9" s="79" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="13.5" customHeight="1" s="158">
-      <c r="D10" s="83" t="inlineStr">
+    <row r="10" ht="13.5" customHeight="1">
+      <c r="D10" s="72" t="inlineStr">
         <is>
           <t>稼働率</t>
         </is>
       </c>
-      <c r="E10" s="189" t="n">
+      <c r="E10" s="191" t="n">
         <v>0.65</v>
       </c>
-      <c r="F10" s="90" t="n"/>
-    </row>
-    <row r="11" ht="13.5" customHeight="1" s="158">
-      <c r="D11" s="83" t="inlineStr">
+      <c r="F10" s="79" t="n"/>
+    </row>
+    <row r="11" ht="13.5" customHeight="1">
+      <c r="D11" s="72" t="inlineStr">
         <is>
           <t>ADR（客室単価）</t>
         </is>
       </c>
-      <c r="E11" s="89" t="n">
+      <c r="E11" s="78" t="n">
         <v>50000</v>
       </c>
-      <c r="F11" s="90" t="inlineStr">
+      <c r="F11" s="79" t="inlineStr">
         <is>
           <t>円</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="13.5" customHeight="1" s="158">
-      <c r="D12" s="83" t="inlineStr">
+    <row r="12" ht="13.5" customHeight="1">
+      <c r="D12" s="72" t="inlineStr">
         <is>
           <t>宿泊人数/室</t>
         </is>
       </c>
-      <c r="E12" s="190" t="n">
+      <c r="E12" s="192" t="n">
         <v>2</v>
       </c>
-      <c r="F12" s="90" t="inlineStr">
+      <c r="F12" s="79" t="inlineStr">
         <is>
           <t>人</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="13.5" customHeight="1" s="158">
-      <c r="D13" s="85" t="inlineStr">
+    <row r="13" ht="13.5" customHeight="1">
+      <c r="D13" s="74" t="inlineStr">
         <is>
           <t>飲食単価/人</t>
         </is>
       </c>
-      <c r="E13" s="93" t="n">
+      <c r="E13" s="82" t="n">
         <v>6000</v>
       </c>
-      <c r="F13" s="94" t="inlineStr">
+      <c r="F13" s="83" t="inlineStr">
         <is>
           <t>円</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="13.5" customHeight="1" s="158"/>
-    <row r="15" ht="13.5" customHeight="1" s="158"/>
-    <row r="16" ht="13.5" customHeight="1" s="158"/>
-    <row r="17" ht="13.5" customHeight="1" s="158">
-      <c r="D17" s="111" t="inlineStr">
+    <row r="14" ht="13.5" customHeight="1"/>
+    <row r="15" ht="13.5" customHeight="1"/>
+    <row r="16" ht="13.5" customHeight="1"/>
+    <row r="17" ht="13.5" customHeight="1">
+      <c r="D17" s="97" t="inlineStr">
         <is>
           <t>【コストドライバー】</t>
         </is>
       </c>
-      <c r="E17" s="78" t="n"/>
-      <c r="F17" s="78" t="n"/>
-    </row>
-    <row r="18" ht="13.5" customHeight="1" s="158"/>
-    <row r="19" ht="13.5" customHeight="1" s="158">
-      <c r="D19" s="168" t="inlineStr">
+      <c r="E17" s="67" t="n"/>
+      <c r="F17" s="67" t="n"/>
+    </row>
+    <row r="18" ht="13.5" customHeight="1"/>
+    <row r="19" ht="13.5" customHeight="1">
+      <c r="D19" s="68" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="E19" s="168" t="inlineStr">
+      <c r="E19" s="68" t="inlineStr">
         <is>
           <t>値</t>
         </is>
       </c>
-      <c r="F19" s="168" t="inlineStr">
+      <c r="F19" s="68" t="inlineStr">
         <is>
           <t>単位</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="13.5" customHeight="1" s="158">
-      <c r="D20" s="80" t="inlineStr">
+    <row r="20" ht="13.5" customHeight="1">
+      <c r="D20" s="69" t="inlineStr">
         <is>
           <t>変動費率（対売上）</t>
         </is>
       </c>
-      <c r="E20" s="191" t="n">
+      <c r="E20" s="193" t="n">
         <v>0.3</v>
       </c>
-      <c r="F20" s="88" t="n"/>
-    </row>
-    <row r="21" ht="13.5" customHeight="1" s="158">
-      <c r="D21" s="83" t="inlineStr">
+      <c r="F20" s="77" t="n"/>
+    </row>
+    <row r="21" ht="13.5" customHeight="1">
+      <c r="D21" s="72" t="inlineStr">
         <is>
           <t>人件費（固定・年）</t>
         </is>
       </c>
-      <c r="E21" s="89" t="n">
+      <c r="E21" s="78" t="n">
         <v>60000000</v>
       </c>
-      <c r="F21" s="90" t="inlineStr">
+      <c r="F21" s="79" t="inlineStr">
         <is>
           <t>円</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="13.5" customHeight="1" s="158">
-      <c r="D22" s="85" t="inlineStr">
+    <row r="22" ht="13.5" customHeight="1">
+      <c r="D22" s="74" t="inlineStr">
         <is>
           <t>その他固定費（年）</t>
         </is>
       </c>
-      <c r="E22" s="93" t="n">
+      <c r="E22" s="82" t="n">
         <v>48000000</v>
       </c>
-      <c r="F22" s="94" t="inlineStr">
+      <c r="F22" s="83" t="inlineStr">
         <is>
           <t>円</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="13.5" customHeight="1" s="158"/>
-    <row r="24" ht="13.5" customHeight="1" s="158">
+    <row r="23" ht="13.5" customHeight="1"/>
+    <row r="24" ht="13.5" customHeight="1">
       <c r="D24" s="3" t="inlineStr">
         <is>
           <t>※ 青字＝手入力の前提。黒字＝数式。緑字＝他シート参照（②③で使用）。</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="13.5" customHeight="1" s="158"/>
+    <row r="25" ht="13.5" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1817,350 +1831,350 @@
   <dimension ref="B2:F32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13"/>
   <cols>
-    <col width="2.36328125" customWidth="1" style="158" min="1" max="3"/>
-    <col width="30" customWidth="1" style="158" min="4" max="4"/>
-    <col width="16" customWidth="1" style="158" min="5" max="5"/>
-    <col width="34" customWidth="1" style="158" min="6" max="6"/>
+    <col width="2.36328125" customWidth="1" min="1" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="2" ht="19.5" customHeight="1" s="158">
-      <c r="B2" s="75" t="inlineStr">
+    <row r="2" ht="19.5" customHeight="1">
+      <c r="B2" s="64" t="inlineStr">
         <is>
           <t>2-4. PLシミュレーション ②計算（Inputを参照して積み上げ）</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="13.5" customHeight="1" s="158"/>
-    <row r="4" ht="13.5" customHeight="1" s="158">
+    <row r="3" ht="13.5" customHeight="1"/>
+    <row r="4" ht="13.5" customHeight="1">
       <c r="D4" s="3" t="inlineStr">
         <is>
           <t>重要！：原則、青字、緑字、黒字を1セルにごっちゃにして計算しない。</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="13.5" customHeight="1" s="158">
-      <c r="D5" s="77" t="inlineStr">
+    <row r="5" ht="13.5" customHeight="1">
+      <c r="D5" s="66" t="inlineStr">
         <is>
           <t>客室・飲食売上の積み上げ</t>
         </is>
       </c>
-      <c r="E5" s="78" t="n"/>
-      <c r="F5" s="78" t="n"/>
-    </row>
-    <row r="6" ht="13.5" customHeight="1" s="158"/>
-    <row r="7" ht="13.5" customHeight="1" s="158">
-      <c r="D7" s="168" t="inlineStr">
+      <c r="E5" s="67" t="n"/>
+      <c r="F5" s="67" t="n"/>
+    </row>
+    <row r="6" ht="13.5" customHeight="1"/>
+    <row r="7" ht="13.5" customHeight="1">
+      <c r="D7" s="68" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="E7" s="168" t="inlineStr">
+      <c r="E7" s="68" t="inlineStr">
         <is>
           <t>金額(円)</t>
         </is>
       </c>
-      <c r="F7" s="168" t="inlineStr">
+      <c r="F7" s="68" t="inlineStr">
         <is>
           <t>計算の内容</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="13.5" customHeight="1" s="158">
-      <c r="D8" s="115" t="inlineStr">
+    <row r="8" ht="13.5" customHeight="1">
+      <c r="D8" s="101" t="inlineStr">
         <is>
           <t>客室数</t>
         </is>
       </c>
-      <c r="E8" s="114">
+      <c r="E8" s="100">
         <f>'2-4_PL①Input'!E8</f>
         <v/>
       </c>
-      <c r="F8" s="115" t="inlineStr">
+      <c r="F8" s="101" t="inlineStr">
         <is>
           <t>Inputシートより</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="13.5" customHeight="1" s="158">
-      <c r="D9" s="118" t="inlineStr">
+    <row r="9" ht="13.5" customHeight="1">
+      <c r="D9" s="104" t="inlineStr">
         <is>
           <t>営業日数</t>
         </is>
       </c>
-      <c r="E9" s="119">
+      <c r="E9" s="105">
         <f>'2-4_PL①Input'!E9</f>
         <v/>
       </c>
-      <c r="F9" s="118" t="inlineStr">
+      <c r="F9" s="104" t="inlineStr">
         <is>
           <t>Inputシートより</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="13.5" customHeight="1" s="158">
-      <c r="D10" s="120" t="inlineStr">
+    <row r="10" ht="13.5" customHeight="1">
+      <c r="D10" s="106" t="inlineStr">
         <is>
           <t>稼働率</t>
         </is>
       </c>
-      <c r="E10" s="192">
+      <c r="E10" s="194">
         <f>'2-4_PL①Input'!E10</f>
         <v/>
       </c>
-      <c r="F10" s="120" t="inlineStr">
+      <c r="F10" s="106" t="inlineStr">
         <is>
           <t>Inputシートより</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="13.5" customHeight="1" s="158">
-      <c r="D11" s="171" t="inlineStr">
+    <row r="11" ht="13.5" customHeight="1">
+      <c r="D11" s="112" t="inlineStr">
         <is>
           <t>稼働室数（室・年）</t>
         </is>
       </c>
-      <c r="E11" s="135">
+      <c r="E11" s="119">
         <f>E8*E9*E10</f>
         <v/>
       </c>
-      <c r="F11" s="128" t="inlineStr">
+      <c r="F11" s="113" t="inlineStr">
         <is>
           <t>客室数×営業日数×稼働率</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="13.5" customHeight="1" s="158"/>
-    <row r="13" ht="13.5" customHeight="1" s="158">
-      <c r="D13" s="130">
+    <row r="12" ht="13.5" customHeight="1"/>
+    <row r="13" ht="13.5" customHeight="1">
+      <c r="D13" s="115">
         <f>'2-4_PL①Input'!$D$11</f>
         <v/>
       </c>
-      <c r="E13" s="131">
+      <c r="E13" s="116">
         <f>'2-4_PL①Input'!E11</f>
         <v/>
       </c>
-      <c r="F13" s="82" t="inlineStr">
+      <c r="F13" s="71" t="inlineStr">
         <is>
           <t>Inputシートより</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="13.5" customHeight="1" s="158">
-      <c r="D14" s="124" t="inlineStr">
+    <row r="14" ht="13.5" customHeight="1">
+      <c r="D14" s="109" t="inlineStr">
         <is>
           <t>客室売上</t>
         </is>
       </c>
-      <c r="E14" s="136">
+      <c r="E14" s="120">
         <f>E11*E13</f>
         <v/>
       </c>
-      <c r="F14" s="124" t="inlineStr">
+      <c r="F14" s="109" t="inlineStr">
         <is>
           <t>販売室数×ADR</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="13.5" customHeight="1" s="158">
-      <c r="D15" s="124" t="n"/>
-      <c r="E15" s="136" t="n"/>
-      <c r="F15" s="124" t="n"/>
-    </row>
-    <row r="16" ht="13.5" customHeight="1" s="158">
-      <c r="D16" s="116" t="inlineStr">
+    <row r="15" ht="13.5" customHeight="1">
+      <c r="D15" s="109" t="n"/>
+      <c r="E15" s="120" t="n"/>
+      <c r="F15" s="109" t="n"/>
+    </row>
+    <row r="16" ht="13.5" customHeight="1">
+      <c r="D16" s="102" t="inlineStr">
         <is>
           <t>宿泊人数/室</t>
         </is>
       </c>
-      <c r="E16" s="193">
+      <c r="E16" s="195">
         <f>'2-4_PL①Input'!E12</f>
         <v/>
       </c>
-      <c r="F16" s="80" t="inlineStr">
+      <c r="F16" s="69" t="inlineStr">
         <is>
           <t>Inputシートより</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="13.5" customHeight="1" s="158">
-      <c r="D17" s="132">
+    <row r="17" ht="13.5" customHeight="1">
+      <c r="D17" s="117">
         <f>'2-4_PL①Input'!$D$13</f>
         <v/>
       </c>
-      <c r="E17" s="133">
+      <c r="E17" s="118">
         <f>'2-4_PL①Input'!E13</f>
         <v/>
       </c>
-      <c r="F17" s="85" t="inlineStr">
+      <c r="F17" s="74" t="inlineStr">
         <is>
           <t>Inputシートより</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="13.5" customHeight="1" s="158">
-      <c r="D18" s="124" t="inlineStr">
+    <row r="18" ht="13.5" customHeight="1">
+      <c r="D18" s="109" t="inlineStr">
         <is>
           <t>飲食売上</t>
         </is>
       </c>
-      <c r="E18" s="136">
+      <c r="E18" s="120">
         <f>E11*E16*E17</f>
         <v/>
       </c>
-      <c r="F18" s="122" t="inlineStr">
+      <c r="F18" s="7" t="inlineStr">
         <is>
           <t>稼働室数x宿泊人数/室×飲食単価/人</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="13.5" customHeight="1" s="158">
-      <c r="D19" s="124" t="n"/>
-      <c r="E19" s="136" t="n"/>
-      <c r="F19" s="124" t="n"/>
-    </row>
-    <row r="20" ht="13.5" customHeight="1" s="158">
-      <c r="D20" s="143" t="inlineStr">
+    <row r="19" ht="13.5" customHeight="1">
+      <c r="D19" s="109" t="n"/>
+      <c r="E19" s="120" t="n"/>
+      <c r="F19" s="109" t="n"/>
+    </row>
+    <row r="20" ht="13.5" customHeight="1">
+      <c r="D20" s="127" t="inlineStr">
         <is>
           <t>売上高 計</t>
         </is>
       </c>
-      <c r="E20" s="144">
+      <c r="E20" s="128">
         <f>E14+E18</f>
         <v/>
       </c>
-      <c r="F20" s="145" t="inlineStr">
+      <c r="F20" s="129" t="inlineStr">
         <is>
           <t>客室売上＋飲食売上</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="13.5" customHeight="1" s="158">
-      <c r="D21" s="124" t="n"/>
-      <c r="E21" s="124" t="n"/>
-      <c r="F21" s="124" t="n"/>
-    </row>
-    <row r="22" ht="13.5" customHeight="1" s="158">
-      <c r="D22" s="122" t="inlineStr">
+    <row r="21" ht="13.5" customHeight="1">
+      <c r="D21" s="109" t="n"/>
+      <c r="E21" s="109" t="n"/>
+      <c r="F21" s="109" t="n"/>
+    </row>
+    <row r="22" ht="13.5" customHeight="1">
+      <c r="D22" s="7" t="inlineStr">
         <is>
           <t>変動費率</t>
         </is>
       </c>
-      <c r="E22" s="194">
+      <c r="E22" s="196">
         <f>'2-4_PL①Input'!E20</f>
         <v/>
       </c>
-      <c r="F22" s="124" t="inlineStr">
+      <c r="F22" s="109" t="inlineStr">
         <is>
           <t>Inputシートより</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="13.5" customHeight="1" s="158">
-      <c r="D23" s="124" t="inlineStr">
+    <row r="23" ht="13.5" customHeight="1">
+      <c r="D23" s="109" t="inlineStr">
         <is>
           <t>変動費</t>
         </is>
       </c>
-      <c r="E23" s="136">
+      <c r="E23" s="120">
         <f>E20*E22</f>
         <v/>
       </c>
-      <c r="F23" s="124" t="inlineStr">
+      <c r="F23" s="109" t="inlineStr">
         <is>
           <t>売上高×変動費率</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="13.5" customHeight="1" s="158">
-      <c r="D24" s="146" t="inlineStr">
+    <row r="24" ht="13.5" customHeight="1">
+      <c r="D24" s="130" t="inlineStr">
         <is>
           <t>限界利益</t>
         </is>
       </c>
-      <c r="E24" s="147">
+      <c r="E24" s="131">
         <f>E20-E23</f>
         <v/>
       </c>
-      <c r="F24" s="148" t="inlineStr">
+      <c r="F24" s="132" t="inlineStr">
         <is>
           <t>売上高−変動費</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="13.5" customHeight="1" s="158">
-      <c r="D25" s="124" t="n"/>
-      <c r="E25" s="140" t="n"/>
-      <c r="F25" s="124" t="n"/>
-    </row>
-    <row r="26" ht="13.5" customHeight="1" s="158">
-      <c r="D26" s="80">
+    <row r="25" ht="13.5" customHeight="1">
+      <c r="D25" s="109" t="n"/>
+      <c r="E25" s="124" t="n"/>
+      <c r="F25" s="109" t="n"/>
+    </row>
+    <row r="26" ht="13.5" customHeight="1">
+      <c r="D26" s="69">
         <f>'2-4_PL①Input'!D21</f>
         <v/>
       </c>
-      <c r="E26" s="114">
+      <c r="E26" s="100">
         <f>'2-4_PL①Input'!E21</f>
         <v/>
       </c>
-      <c r="F26" s="80" t="n"/>
-    </row>
-    <row r="27" ht="13.5" customHeight="1" s="158">
-      <c r="D27" s="85">
+      <c r="F26" s="69" t="n"/>
+    </row>
+    <row r="27" ht="13.5" customHeight="1">
+      <c r="D27" s="74">
         <f>'2-4_PL①Input'!D22</f>
         <v/>
       </c>
-      <c r="E27" s="142">
+      <c r="E27" s="126">
         <f>'2-4_PL①Input'!E22</f>
         <v/>
       </c>
-      <c r="F27" s="85" t="n"/>
-    </row>
-    <row r="28" ht="13.5" customHeight="1" s="158">
-      <c r="D28" s="151" t="inlineStr">
+      <c r="F27" s="74" t="n"/>
+    </row>
+    <row r="28" ht="13.5" customHeight="1">
+      <c r="D28" s="135" t="inlineStr">
         <is>
           <t>固定費 計</t>
         </is>
       </c>
-      <c r="E28" s="152">
+      <c r="E28" s="136">
         <f>SUM(E26:E27)</f>
         <v/>
       </c>
-      <c r="F28" s="153" t="inlineStr">
+      <c r="F28" s="137" t="inlineStr">
         <is>
           <t>人件費＋その他固定費</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="13.5" customHeight="1" s="158">
-      <c r="D29" s="124" t="n"/>
-      <c r="E29" s="136" t="n"/>
-      <c r="F29" s="124" t="n"/>
-    </row>
-    <row r="30" ht="13.5" customHeight="1" s="158">
-      <c r="D30" s="143" t="inlineStr">
+    <row r="29" ht="13.5" customHeight="1">
+      <c r="D29" s="109" t="n"/>
+      <c r="E29" s="120" t="n"/>
+      <c r="F29" s="109" t="n"/>
+    </row>
+    <row r="30" ht="13.5" customHeight="1">
+      <c r="D30" s="127" t="inlineStr">
         <is>
           <t>営業利益</t>
         </is>
       </c>
-      <c r="E30" s="149">
+      <c r="E30" s="133">
         <f>E24-E28</f>
         <v/>
       </c>
-      <c r="F30" s="150" t="inlineStr">
+      <c r="F30" s="134" t="inlineStr">
         <is>
           <t>限界利益−固定費</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="13.5" customHeight="1" s="158"/>
-    <row r="32" ht="13.5" customHeight="1" s="158">
+    <row r="31" ht="13.5" customHeight="1"/>
+    <row r="32" ht="13.5" customHeight="1">
       <c r="D32" s="3" t="inlineStr">
         <is>
           <t>緑字＝①Inputへの参照。黄色＝主要な中間・最終アウトプット。</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="13.5" customHeight="1" s="158"/>
-    <row r="34" ht="13.5" customHeight="1" s="158"/>
+    <row r="33" ht="13.5" customHeight="1"/>
+    <row r="34" ht="13.5" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2175,148 +2189,148 @@
   <dimension ref="B2:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13"/>
   <cols>
-    <col width="2.36328125" customWidth="1" style="158" min="1" max="3"/>
-    <col width="23.453125" customWidth="1" style="158" min="4" max="4"/>
-    <col width="18" customWidth="1" style="158" min="5" max="5"/>
-    <col width="12" customWidth="1" style="158" min="6" max="6"/>
+    <col width="2.36328125" customWidth="1" min="1" max="3"/>
+    <col width="23.453125" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="2" ht="19.5" customHeight="1" s="158">
-      <c r="B2" s="75" t="inlineStr">
+    <row r="2" ht="19.5" customHeight="1">
+      <c r="B2" s="64" t="inlineStr">
         <is>
           <t>2-4. PLシミュレーション ③Output（PLサマリ）</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="13.5" customHeight="1" s="158"/>
-    <row r="4" ht="13.5" customHeight="1" s="158">
+    <row r="3" ht="13.5" customHeight="1"/>
+    <row r="4" ht="13.5" customHeight="1">
       <c r="D4" s="3" t="inlineStr">
         <is>
           <t>PPTに張り付けるサマリなどは、数字の色を付けません。</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="13.5" customHeight="1" s="158">
-      <c r="D5" s="77" t="inlineStr">
+    <row r="5" ht="13.5" customHeight="1">
+      <c r="D5" s="66" t="inlineStr">
         <is>
           <t>年間 損益計算書（サマリ）</t>
         </is>
       </c>
-      <c r="E5" s="78" t="n"/>
-      <c r="F5" s="78" t="n"/>
-    </row>
-    <row r="6" ht="13.5" customHeight="1" s="158">
-      <c r="D6" s="165" t="inlineStr">
+      <c r="E5" s="67" t="n"/>
+      <c r="F5" s="67" t="n"/>
+    </row>
+    <row r="6" ht="13.5" customHeight="1">
+      <c r="D6" s="145" t="inlineStr">
         <is>
           <t>単位：　百万円</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="13.5" customHeight="1" s="158"/>
-    <row r="8" ht="13.5" customHeight="1" s="158">
-      <c r="D8" s="168" t="inlineStr">
+    <row r="7" ht="13.5" customHeight="1"/>
+    <row r="8" ht="13.5" customHeight="1">
+      <c r="D8" s="68" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="E8" s="154" t="inlineStr">
+      <c r="E8" s="138" t="inlineStr">
         <is>
           <t>金額</t>
         </is>
       </c>
-      <c r="F8" s="154" t="inlineStr">
+      <c r="F8" s="138" t="inlineStr">
         <is>
           <t>対売上%</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="13.5" customHeight="1" s="158">
-      <c r="D9" s="128" t="inlineStr">
+    <row r="9" ht="13.5" customHeight="1">
+      <c r="D9" s="113" t="inlineStr">
         <is>
           <t>売上高</t>
         </is>
       </c>
-      <c r="E9" s="195">
+      <c r="E9" s="197">
         <f>'2-4_PL②計算'!E20/10^6</f>
         <v/>
       </c>
-      <c r="F9" s="196">
+      <c r="F9" s="198">
         <f>E9/$E$9</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="13.5" customHeight="1" s="158"/>
-    <row r="11" ht="13.5" customHeight="1" s="158">
-      <c r="D11" s="129" t="inlineStr">
+    <row r="10" ht="13.5" customHeight="1"/>
+    <row r="11" ht="13.5" customHeight="1">
+      <c r="D11" s="114" t="inlineStr">
         <is>
           <t>変動費</t>
         </is>
       </c>
-      <c r="E11" s="197">
+      <c r="E11" s="199">
         <f>'2-4_PL②計算'!E23/10^6</f>
         <v/>
       </c>
-      <c r="F11" s="198">
+      <c r="F11" s="200">
         <f>-E11/$E$9</f>
         <v/>
       </c>
     </row>
-    <row r="12" ht="13.5" customHeight="1" s="158">
-      <c r="D12" s="171" t="inlineStr">
+    <row r="12" ht="13.5" customHeight="1">
+      <c r="D12" s="112" t="inlineStr">
         <is>
           <t>限界利益</t>
         </is>
       </c>
-      <c r="E12" s="195">
+      <c r="E12" s="197">
         <f>E9-E11</f>
         <v/>
       </c>
-      <c r="F12" s="199">
+      <c r="F12" s="201">
         <f>E12/$E$9</f>
         <v/>
       </c>
     </row>
-    <row r="13" ht="13.5" customHeight="1" s="158"/>
-    <row r="14" ht="13.5" customHeight="1" s="158">
-      <c r="D14" s="129" t="inlineStr">
+    <row r="13" ht="13.5" customHeight="1"/>
+    <row r="14" ht="13.5" customHeight="1">
+      <c r="D14" s="114" t="inlineStr">
         <is>
           <t>固定費</t>
         </is>
       </c>
-      <c r="E14" s="197">
+      <c r="E14" s="199">
         <f>'2-4_PL②計算'!E28/10^6</f>
         <v/>
       </c>
-      <c r="F14" s="198">
+      <c r="F14" s="200">
         <f>-E14/$E$9</f>
         <v/>
       </c>
     </row>
-    <row r="15" ht="13.5" customHeight="1" s="158">
-      <c r="D15" s="143" t="inlineStr">
+    <row r="15" ht="13.5" customHeight="1">
+      <c r="D15" s="127" t="inlineStr">
         <is>
           <t>営業利益</t>
         </is>
       </c>
-      <c r="E15" s="200">
+      <c r="E15" s="202">
         <f>E12-E14</f>
         <v/>
       </c>
-      <c r="F15" s="201">
+      <c r="F15" s="203">
         <f>E15/$E$9</f>
         <v/>
       </c>
     </row>
-    <row r="16" ht="13.5" customHeight="1" s="158"/>
-    <row r="17" ht="13.5" customHeight="1" s="158">
+    <row r="16" ht="13.5" customHeight="1"/>
+    <row r="17" ht="13.5" customHeight="1">
       <c r="D17" s="3" t="inlineStr">
         <is>
           <t>Input①の青字（稼働率・ADR等）を変えると、この③まで一気に更新されます。</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="13.5" customHeight="1" s="158"/>
-    <row r="19" ht="13.5" customHeight="1" s="158"/>
+    <row r="18" ht="13.5" customHeight="1"/>
+    <row r="19" ht="13.5" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/files/excel-mastery-2-4.xlsx
+++ b/files/excel-mastery-2-4.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-1605" yWindow="-16320" windowWidth="29040" windowHeight="16440" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="280" windowWidth="17320" windowHeight="10400" tabRatio="773" firstSheet="2" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="2-4_PL①Input" sheetId="1" state="visible" r:id="rId1"/>
@@ -555,7 +555,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="204">
+  <cellXfs count="205">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -1051,74 +1051,77 @@
     <xf numFmtId="3" fontId="23" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="13" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="13" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="13" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="13" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="13" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="13" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="13" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="13" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="13" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="13" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="165" fontId="23" fillId="3" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -1687,7 +1690,7 @@
           <t>稼働率</t>
         </is>
       </c>
-      <c r="E10" s="191" t="n">
+      <c r="E10" s="192" t="n">
         <v>0.65</v>
       </c>
       <c r="F10" s="79" t="n"/>
@@ -1713,7 +1716,7 @@
           <t>宿泊人数/室</t>
         </is>
       </c>
-      <c r="E12" s="192" t="n">
+      <c r="E12" s="193" t="n">
         <v>2</v>
       </c>
       <c r="F12" s="79" t="inlineStr">
@@ -1773,7 +1776,7 @@
           <t>変動費率（対売上）</t>
         </is>
       </c>
-      <c r="E20" s="193" t="n">
+      <c r="E20" s="194" t="n">
         <v>0.3</v>
       </c>
       <c r="F20" s="77" t="n"/>
@@ -1917,7 +1920,7 @@
           <t>稼働率</t>
         </is>
       </c>
-      <c r="E10" s="194">
+      <c r="E10" s="195">
         <f>'2-4_PL①Input'!E10</f>
         <v/>
       </c>
@@ -1986,7 +1989,7 @@
           <t>宿泊人数/室</t>
         </is>
       </c>
-      <c r="E16" s="195">
+      <c r="E16" s="196">
         <f>'2-4_PL①Input'!E12</f>
         <v/>
       </c>
@@ -2059,7 +2062,7 @@
           <t>変動費率</t>
         </is>
       </c>
-      <c r="E22" s="196">
+      <c r="E22" s="197">
         <f>'2-4_PL①Input'!E20</f>
         <v/>
       </c>
@@ -2250,11 +2253,11 @@
           <t>売上高</t>
         </is>
       </c>
-      <c r="E9" s="197">
+      <c r="E9" s="198">
         <f>'2-4_PL②計算'!E20/10^6</f>
         <v/>
       </c>
-      <c r="F9" s="198">
+      <c r="F9" s="199">
         <f>E9/$E$9</f>
         <v/>
       </c>
@@ -2266,11 +2269,11 @@
           <t>変動費</t>
         </is>
       </c>
-      <c r="E11" s="199">
+      <c r="E11" s="200">
         <f>'2-4_PL②計算'!E23/10^6</f>
         <v/>
       </c>
-      <c r="F11" s="200">
+      <c r="F11" s="201">
         <f>-E11/$E$9</f>
         <v/>
       </c>
@@ -2281,11 +2284,11 @@
           <t>限界利益</t>
         </is>
       </c>
-      <c r="E12" s="197">
+      <c r="E12" s="198">
         <f>E9-E11</f>
         <v/>
       </c>
-      <c r="F12" s="201">
+      <c r="F12" s="202">
         <f>E12/$E$9</f>
         <v/>
       </c>
@@ -2297,11 +2300,11 @@
           <t>固定費</t>
         </is>
       </c>
-      <c r="E14" s="199">
+      <c r="E14" s="200">
         <f>'2-4_PL②計算'!E28/10^6</f>
         <v/>
       </c>
-      <c r="F14" s="200">
+      <c r="F14" s="201">
         <f>-E14/$E$9</f>
         <v/>
       </c>
@@ -2312,11 +2315,11 @@
           <t>営業利益</t>
         </is>
       </c>
-      <c r="E15" s="202">
+      <c r="E15" s="203">
         <f>E12-E14</f>
         <v/>
       </c>
-      <c r="F15" s="203">
+      <c r="F15" s="204">
         <f>E15/$E$9</f>
         <v/>
       </c>
